--- a/list.xlsx
+++ b/list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saikishi-my.sharepoint.com/personal/t0011_saikishi_onmicrosoft_com/Documents/OneDriveドキュメント/100ex www(outer)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="11_AD4D066CA252ABDACC1048B419D2F48C72EEDF4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{911AF258-6681-410F-9F7F-1A855BD42AEB}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="11_AD4D066CA252ABDACC1048B419D2F48C72EEDF4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F4F2079-C7E1-432B-BE09-9BDEF1D66E20}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="95">
   <si>
     <t>title</t>
   </si>
@@ -39,6 +39,372 @@
     <t>desc</t>
   </si>
   <si>
+    <t>1nen-katachi</t>
+  </si>
+  <si>
+    <t>2nen-tukue</t>
+  </si>
+  <si>
+    <t>clock</t>
+  </si>
+  <si>
+    <t>kakudo</t>
+  </si>
+  <si>
+    <t>kukumeijin</t>
+  </si>
+  <si>
+    <t>menseki-triangle</t>
+  </si>
+  <si>
+    <t>nanbun</t>
+  </si>
+  <si>
+    <t>obento</t>
+  </si>
+  <si>
+    <t>shikitsume</t>
+  </si>
+  <si>
+    <t>stopwatch</t>
+  </si>
+  <si>
+    <t>supatto</t>
+  </si>
+  <si>
+    <t>tenkaizu</t>
+  </si>
+  <si>
+    <t>timer</t>
+  </si>
+  <si>
+    <t>trokko</t>
+  </si>
+  <si>
+    <t>zukeinoyaiba</t>
+  </si>
+  <si>
+    <t>かたちづくり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はいぜんのてつ人２８号</t>
+    <rPh sb="7" eb="8">
+      <t>ジン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とけいをひょうじするだけのアプリ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>角度インベーダー</t>
+    <rPh sb="0" eb="2">
+      <t>カクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>九九めいじん</t>
+    <rPh sb="0" eb="2">
+      <t>クク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三角形の面積</t>
+    <rPh sb="0" eb="3">
+      <t>サンカクケイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>メンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なんぶんのなんなんな</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おべんとう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しきつめーる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストップウォッチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解決！スパット</t>
+    <rPh sb="0" eb="2">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>展開図をつくろう</t>
+    <rPh sb="0" eb="3">
+      <t>テンカイズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイマー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トロッコ学習クイズ</t>
+    <rPh sb="4" eb="6">
+      <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>図形のヤイバ</t>
+    <rPh sb="0" eb="2">
+      <t>ズケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１年算数形作りです</t>
+    <rPh sb="1" eb="2">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カタチヅク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２年算数のプログラミングです。</t>
+    <rPh sb="1" eb="2">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時計を表示するだけのアプリです</t>
+    <rPh sb="0" eb="2">
+      <t>トケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４年算数角度の学習</t>
+    <rPh sb="1" eb="2">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２年算数九九の学習</t>
+    <rPh sb="1" eb="2">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>クク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>５年算数三角形の面積の学習</t>
+    <rPh sb="1" eb="2">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>サンカクケイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メンセキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４・５年算数分数</t>
+    <rPh sb="3" eb="4">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ブンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>低学年向けiPadの使い方を学ぶアプリです</t>
+    <rPh sb="0" eb="3">
+      <t>テイガクネン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小学校算数　しきつめの学習で使います</t>
+    <rPh sb="0" eb="3">
+      <t>ショウガッコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面いっぱいに表示されるストップウォッチ。</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中学校数学　立体図形の作成とせん断</t>
+    <rPh sb="0" eb="3">
+      <t>チュウガッコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>スウガク</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>リッタイズケイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小学校算数　展開図を作成するアプリです</t>
+    <rPh sb="0" eb="3">
+      <t>ショウガッコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>テンカイズ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面いっぱいにタイマーを表示します</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トロッコに乗って、問題を解いていくアプリ</t>
+    <rPh sb="5" eb="6">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小学校の算数で図形の作成、切断、複製、回転などが行える総合アプリです</t>
+    <rPh sb="0" eb="3">
+      <t>ショウガッコウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サンスウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ズケイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツダン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>フクセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ソウゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>grades1</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -76,7 +442,82 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>算数</t>
+    <rPh sb="0" eb="2">
+      <t>サンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数学</t>
+    <rPh sb="0" eb="2">
+      <t>スウガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>tokushi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おはじき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ohajiki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おはじきやブロックを表示します</t>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>100マスオさん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>100masuo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１００ます計算（実際は２５ます）</t>
+    <rPh sb="5" eb="7">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まほうのレジスター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>okane</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お金の両替が学べます</t>
+    <rPh sb="1" eb="2">
+      <t>カネ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リョウガエ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マナ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -104,6 +545,134 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mosaic</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>図工</t>
+    <rPh sb="0" eb="2">
+      <t>ズコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>◯</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モザイク壁画の作成支援ツールです。Excelに出力する機能もあります</t>
+    <rPh sb="4" eb="6">
+      <t>ヘキガ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シエン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モザイクアートメーカー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１０のともだち</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10notomodachi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１０はいくつといくつ？の学習ができます</t>
+    <rPh sb="12" eb="14">
+      <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stick Motion（スティックモーション）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stickmotion</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コマ送りのアニメーションを制作するアプリです。</t>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>saikitoontyping</t>
+  </si>
+  <si>
+    <t>佐伯市にまつわる単語を取り合う、カルタ取りのようなタイピング練習アプリです</t>
+    <rPh sb="0" eb="3">
+      <t>サイキシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>レンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーボード練習</t>
+    <rPh sb="5" eb="7">
+      <t>レンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さいきとぅーんタイピング(ベータ版)</t>
+    <rPh sb="16" eb="17">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ごまだっしゅ！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gomadash</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時計の学習アプリです。</t>
+    <rPh sb="0" eb="2">
+      <t>トケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガクシュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -430,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
@@ -455,81 +1024,679 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="N1" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
+      </c>
+      <c r="O10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" t="s">
+        <v>59</v>
+      </c>
+      <c r="O11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" t="s">
+        <v>59</v>
+      </c>
+      <c r="O14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" t="s">
+        <v>59</v>
+      </c>
+      <c r="K15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" t="s">
+        <v>59</v>
+      </c>
+      <c r="O15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" t="s">
-        <v>16</v>
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" t="s">
+        <v>59</v>
+      </c>
+      <c r="K16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16" t="s">
+        <v>59</v>
+      </c>
+      <c r="O16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" t="s">
+        <v>59</v>
+      </c>
+      <c r="O17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" t="s">
+        <v>59</v>
+      </c>
+      <c r="O18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N19" t="s">
+        <v>59</v>
+      </c>
+      <c r="O19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N20" t="s">
+        <v>59</v>
+      </c>
+      <c r="O20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" t="s">
+        <v>59</v>
+      </c>
+      <c r="O21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s">
+        <v>79</v>
+      </c>
+      <c r="N22" t="s">
+        <v>79</v>
+      </c>
+      <c r="O22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" t="s">
+        <v>79</v>
+      </c>
+      <c r="O23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s">
+        <v>79</v>
+      </c>
+      <c r="I24" t="s">
+        <v>79</v>
+      </c>
+      <c r="J24" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" t="s">
+        <v>79</v>
+      </c>
+      <c r="L24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M24" t="s">
+        <v>79</v>
+      </c>
+      <c r="N24" t="s">
+        <v>79</v>
+      </c>
+      <c r="O24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" t="s">
+        <v>79</v>
+      </c>
+      <c r="O25" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saikishi-my.sharepoint.com/personal/t0011_saikishi_onmicrosoft_com/Documents/OneDriveドキュメント/100ex www(outer)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="262" documentId="11_AD4D066CA252ABDACC1048B419D2F48C72EEDF4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F4F2079-C7E1-432B-BE09-9BDEF1D66E20}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="11_AD4D066CA252ABDACC1048B419D2F48C72EEDF4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33E70CBD-8DCF-4700-9EA6-7FC998A67656}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="0" windowWidth="15375" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>title</t>
   </si>
@@ -490,16 +490,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>１００ます計算（実際は２５ます）</t>
-    <rPh sb="5" eb="7">
-      <t>ケイサン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジッサイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>まほうのレジスター</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -602,24 +592,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Stick Motion（スティックモーション）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>stickmotion</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コマ送りのアニメーションを制作するアプリです。</t>
-    <rPh sb="2" eb="3">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>セイサク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>saikitoontyping</t>
   </si>
   <si>
@@ -673,6 +645,19 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１００ます計算（実際は２５ます） ※アッシュさんの１００マス夫さんをリメイクしました（https://www.vector.co.jp/soft/win95/edu/se184918.html）</t>
+    <rPh sb="5" eb="7">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>オット</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -734,6 +719,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -999,7 +988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
@@ -1469,7 +1458,7 @@
         <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
         <v>59</v>
@@ -1507,13 +1496,13 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
         <v>70</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
         <v>71</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
       </c>
       <c r="F19" t="s">
         <v>59</v>
@@ -1527,14 +1516,14 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" t="s">
         <v>74</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>75</v>
       </c>
-      <c r="D20" t="s">
-        <v>76</v>
-      </c>
       <c r="E20" t="s">
         <v>59</v>
       </c>
@@ -1566,56 +1555,56 @@
         <v>59</v>
       </c>
       <c r="O20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" t="s">
+        <v>59</v>
+      </c>
+      <c r="O21" t="s">
         <v>77</v>
-      </c>
-      <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="I21" t="s">
-        <v>79</v>
-      </c>
-      <c r="J21" t="s">
-        <v>59</v>
-      </c>
-      <c r="K21" t="s">
-        <v>59</v>
-      </c>
-      <c r="L21" t="s">
-        <v>59</v>
-      </c>
-      <c r="M21" t="s">
-        <v>59</v>
-      </c>
-      <c r="O21" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s">
         <v>82</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>83</v>
       </c>
-      <c r="D22" t="s">
-        <v>84</v>
-      </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O22" t="s">
         <v>60</v>
@@ -1623,79 +1612,62 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
         <v>85</v>
       </c>
-      <c r="B23" t="s">
+      <c r="G23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s">
+        <v>78</v>
+      </c>
+      <c r="I23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" t="s">
+        <v>78</v>
+      </c>
+      <c r="L23" t="s">
+        <v>78</v>
+      </c>
+      <c r="M23" t="s">
+        <v>78</v>
+      </c>
+      <c r="N23" t="s">
+        <v>78</v>
+      </c>
+      <c r="O23" t="s">
         <v>86</v>
-      </c>
-      <c r="D23" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" t="s">
-        <v>79</v>
-      </c>
-      <c r="O23" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="E24" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" t="s">
+        <v>78</v>
       </c>
       <c r="G24" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" t="s">
-        <v>79</v>
-      </c>
-      <c r="I24" t="s">
-        <v>79</v>
-      </c>
-      <c r="J24" t="s">
-        <v>79</v>
-      </c>
-      <c r="K24" t="s">
-        <v>79</v>
-      </c>
-      <c r="L24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M24" t="s">
-        <v>79</v>
-      </c>
-      <c r="N24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" t="s">
-        <v>79</v>
-      </c>
-      <c r="O25" t="s">
         <v>60</v>
       </c>
     </row>

--- a/list.xlsx
+++ b/list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saikishi-my.sharepoint.com/personal/t0011_saikishi_onmicrosoft_com/Documents/OneDriveドキュメント/100ex www(outer)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="11_AD4D066CA252ABDACC1048B419D2F48C72EEDF4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33E70CBD-8DCF-4700-9EA6-7FC998A67656}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C74CA03-677A-4304-846F-ED1ADA66BAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="0" windowWidth="15375" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="96">
   <si>
     <t>title</t>
   </si>
@@ -659,6 +659,25 @@
     <rPh sb="30" eb="31">
       <t>オット</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bibliotimer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビブリオタイマーです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>図書</t>
+    <rPh sb="0" eb="2">
+      <t>トショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビブリオタイマー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -719,10 +738,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -988,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
@@ -1671,6 +1686,35 @@
         <v>60</v>
       </c>
     </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" t="s">
+        <v>78</v>
+      </c>
+      <c r="J25" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" t="s">
+        <v>78</v>
+      </c>
+      <c r="L25" t="s">
+        <v>78</v>
+      </c>
+      <c r="M25" t="s">
+        <v>78</v>
+      </c>
+      <c r="O25" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/list.xlsx
+++ b/list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saikishi-my.sharepoint.com/personal/t0011_saikishi_onmicrosoft_com/Documents/OneDriveドキュメント/100ex www(outer)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C74CA03-677A-4304-846F-ED1ADA66BAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{4C74CA03-677A-4304-846F-ED1ADA66BAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81D074CE-2478-42FA-AFD6-1EFC8248F8E2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="100">
   <si>
     <t>title</t>
   </si>
@@ -678,6 +678,31 @@
   </si>
   <si>
     <t>ビブリオタイマー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロボ相撲</t>
+    <rPh sb="2" eb="4">
+      <t>スモウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>robosumou</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロボットをプログラミングして相撲をとるアプリです。</t>
+    <rPh sb="14" eb="16">
+      <t>スモウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技術</t>
+    <rPh sb="0" eb="2">
+      <t>ギジュツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -738,6 +763,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1003,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
@@ -1715,6 +1744,35 @@
         <v>94</v>
       </c>
     </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" t="s">
+        <v>78</v>
+      </c>
+      <c r="J26" t="s">
+        <v>78</v>
+      </c>
+      <c r="K26" t="s">
+        <v>78</v>
+      </c>
+      <c r="L26" t="s">
+        <v>78</v>
+      </c>
+      <c r="M26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O26" t="s">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/list.xlsx
+++ b/list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saikishi-my.sharepoint.com/personal/t0011_saikishi_onmicrosoft_com/Documents/OneDriveドキュメント/100ex www(outer)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{4C74CA03-677A-4304-846F-ED1ADA66BAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81D074CE-2478-42FA-AFD6-1EFC8248F8E2}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{4C74CA03-677A-4304-846F-ED1ADA66BAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EECAB90-9453-4656-A2FD-20C23249DED2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="104">
   <si>
     <t>title</t>
   </si>
@@ -702,6 +702,34 @@
     <t>技術</t>
     <rPh sb="0" eb="2">
       <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>りずむクエスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>seikatsu</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生活習慣をみなおすアプリです。</t>
+    <rPh sb="0" eb="2">
+      <t>セイカツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュウカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保健・学級活動</t>
+    <rPh sb="0" eb="2">
+      <t>ホケン</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ガッキュウカツドウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -763,10 +791,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1032,15 +1056,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="71.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="71.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1773,6 +1797,35 @@
         <v>99</v>
       </c>
     </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" t="s">
+        <v>78</v>
+      </c>
+      <c r="J27" t="s">
+        <v>78</v>
+      </c>
+      <c r="K27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L27" t="s">
+        <v>78</v>
+      </c>
+      <c r="M27" t="s">
+        <v>78</v>
+      </c>
+      <c r="O27" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
